--- a/Data_Table/고양이 캐릭터 테이블.xlsx
+++ b/Data_Table/고양이 캐릭터 테이블.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Character" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Skill" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cond_Type" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Effect_Type" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Character" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cond_Type" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effect_Type" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.75" customWidth="1" min="1" max="1"/>
@@ -473,7 +473,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>체류 시간</t>
+          <t>체류 시간 (안 씀)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -488,10 +488,15 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>무리 스킬</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>캐릭터 설명</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>에셋 폴더</t>
         </is>
@@ -545,10 +550,15 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
+          <t>crowd_skill</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
           <t>character_desc</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>asset_folder</t>
         </is>
@@ -602,10 +612,15 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -645,12 +660,15 @@
       <c r="I4" s="1" t="n">
         <v>50001</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="1" t="n">
+        <v>50011</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>동네 어디에나 있는 치즈 태비. 평범하게 부수고, 평범하게 귀엽다.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/cheese</t>
         </is>
@@ -690,12 +708,15 @@
       <c r="I5" s="1" t="n">
         <v>50002</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="1" t="n">
+        <v>50012</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>조용하고 우아하게… 그리고 아주 빠르게 컵을 민다.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/mackerel</t>
         </is>
@@ -735,12 +756,15 @@
       <c r="I6" s="1" t="n">
         <v>50003</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="1" t="n">
+        <v>50013</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>태어날 때부터 정장 차림. 급소만 골라 친다.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/tuxedo</t>
         </is>
@@ -780,12 +804,15 @@
       <c r="I7" s="1" t="n">
         <v>50004</v>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="1" t="n">
+        <v>50014</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>털이 너무 많아서 움직이기 싫다. 대신 앉으면 다 부서진다.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/chonk</t>
         </is>
@@ -825,12 +852,15 @@
       <c r="I8" s="1" t="n">
         <v>50005</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="1" t="n">
+        <v>50015</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>다리가 짧아서 걷는 것보다 구르는 게 빠르다.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/loaf</t>
         </is>
@@ -870,12 +900,15 @@
       <c r="I9" s="1" t="n">
         <v>50006</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="1" t="n">
+        <v>50016</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>야생의 피가 흐른다. 눈 깜짝할 새 옆에 와 있다.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/ninja</t>
         </is>
@@ -915,12 +948,15 @@
       <c r="I10" s="1" t="n">
         <v>50007</v>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="1" t="n">
+        <v>50017</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>털이 없는 대신 눈빛이 너무 강렬해서 물건이 깨진다.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/laser</t>
         </is>
@@ -960,12 +996,15 @@
       <c r="I11" s="1" t="n">
         <v>50008</v>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="1" t="n">
+        <v>50018</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>고양이계의 헤비급. 앞발 한 번이면 식탁이 흔들린다.</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/gym</t>
         </is>
@@ -1005,12 +1044,15 @@
       <c r="I12" s="1" t="n">
         <v>50009</v>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="1" t="n">
+        <v>50019</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>할로윈 모자를 쓰더니 진짜로 마법을 쓰기 시작했다.</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/fire</t>
         </is>
@@ -1050,12 +1092,15 @@
       <c r="I13" s="1" t="n">
         <v>50010</v>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="1" t="n">
+        <v>50020</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>어디서 우주복을 구했는지는 아무도 모른다. 무중력으로 에너지를 모은다.</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/space</t>
         </is>
@@ -1072,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2097,6 +2142,676 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>50011</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>냥냥 대폭격</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Slam</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>쥐가 가장 많이 모인 곳으로 뛰어올라 내려찍기, 범위 안 쥐 기절</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>50012</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>냥펀치 연타</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Combo</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>무리를 찾아 작은 내려찍기 3연속 (매번 새 무리를 노림)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>50013</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>급소 찌르기</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Pinpoint</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>좁지만 아주 빠르게, 오래 기절시키는 일격</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>50014</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>뱃살 프레스</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Belly</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>아주 넓은 범위를 뱃살로 깔아뭉갬, 물건도 날아감</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>50015</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>식빵 볼링</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Roll</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>950</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>무리를 향해 데굴데굴 굴러 지나가는 쥐를 쓰러뜨리고 끝에서 쿵</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>50016</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>그림자 습격</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Blink</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>연기처럼 사라졌다가 무리 한가운데 나타나 내려찍기 (거리 무관)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>50017</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>레이저 폭격</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Laser</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="1" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>가만히 서서 쥐가 많은 곳 2군데에 하늘 레이저</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>50018</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>지진 내려찍기</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Quake</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>내려찍은 자리에서 충격파가 3겹으로 퍼짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>50019</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>운석 마법</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Meteor</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>쥐가 많은 곳 3군데에 운석 소환</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>50020</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>블랙홀</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Vortex</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>520</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>무리 한가운데 블랙홀 → 쥐를 빨아들인 뒤 띄워서 기절</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2238,7 +2953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2797,6 +3512,426 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Slam</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>무리 내려찍기 (경고 원 → 웅크림 → 도약 → 착지 범위 기절)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>범위 반경</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>기절 (초)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>웅크림 (초)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>체공 (초)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Combo</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>작은 내려찍기 연속 (매번 새 무리)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>범위 반경</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>기절 (초)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>웅크림 (초)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>연속 횟수</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>다음까지 간격 (초)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Pinpoint</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>좁고 빠른 내려찍기 (긴 기절)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>범위 반경</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>기절 (초)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>웅크림 (초)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>체공 (초)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Belly</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>넓은 깔아뭉개기 + 물건 날림</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>범위 반경</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>기절 (초)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>웅크림 (초)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>체공 (초)</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>물건 날리는 속도</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Roll</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>무리로 굴러가며 길 위 쥐 기절 + 끝에서 범위 기절</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>끝 범위 반경</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>기절 (초)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>웅크림 (초)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>길 폭</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>굴러가는 속도</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Blink</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>사라졌다가 무리 한가운데 나타나 내려찍기</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>범위 반경</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>기절 (초)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>웅크림 (초)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Laser</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>제자리에서 무리 여러 곳에 하늘 레이저</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>범위 반경</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>기절 (초)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>경고 (초)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>노리는 곳 수</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Quake</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>내려찍기 + 충격파 여러 겹</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>첫 고리 반경</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>기절 (초)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>웅크림 (초)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>고리 수</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>고리마다 늘어나는 반경</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>고리 간격 (초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Meteor</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>무리 여러 곳에 운석</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>범위 반경</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>기절 (초)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>경고 (초)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>노리는 곳 수</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Crowd_Vortex</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>블랙홀로 빨아들인 뒤 띄워 기절</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>범위 반경</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>기절 (초)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>경고 (초)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>빨아들이는 속도</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data_Table/고양이 캐릭터 테이블.xlsx
+++ b/Data_Table/고양이 캐릭터 테이블.xlsx
@@ -424,12 +424,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.75" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -453,50 +453,55 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>캐릭터 이름 키</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>코드 id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>첫 등장 층</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>체력 배율</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>체류 시간 (안 씀)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>크기 배율</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>스킬</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>무리 스킬</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>캐릭터 설명</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>에셋 폴더</t>
         </is>
@@ -515,50 +520,55 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t>character_name_sk</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t>code_id</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>cat_category</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>spawn_floor</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>hp_mul</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>life_time</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>size_mul</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>skill</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>crowd_skill</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>character_desc</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>asset_folder</t>
         </is>
@@ -577,50 +587,55 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -635,40 +650,43 @@
           <t>코리안 숏헤어</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>2140001</v>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>cheese</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="F4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="G4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="H4" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="J4" s="1" t="n">
         <v>50001</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="K4" s="1" t="n">
         <v>50011</v>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>동네 어디에나 있는 치즈 태비. 평범하게 부수고, 평범하게 귀엽다.</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/cheese</t>
         </is>
@@ -683,40 +701,43 @@
           <t>러시안 블루</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="n">
+        <v>2140002</v>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>mackerel</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="F5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="G5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="H5" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="I5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="J5" s="1" t="n">
         <v>50002</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="K5" s="1" t="n">
         <v>50012</v>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>조용하고 우아하게… 그리고 아주 빠르게 컵을 민다.</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/mackerel</t>
         </is>
@@ -731,40 +752,43 @@
           <t>턱시도</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>2140003</v>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>tuxedo</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="F6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="H6" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="I6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="J6" s="1" t="n">
         <v>50003</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="K6" s="1" t="n">
         <v>50013</v>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>태어날 때부터 정장 차림. 급소만 골라 친다.</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/tuxedo</t>
         </is>
@@ -779,40 +803,43 @@
           <t>페르시안</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="2" t="n">
+        <v>2140004</v>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>chonk</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="F7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="H7" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="I7" s="1" t="n">
         <v>1.12</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>50004</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="K7" s="1" t="n">
         <v>50014</v>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>털이 너무 많아서 움직이기 싫다. 대신 앉으면 다 부서진다.</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/chonk</t>
         </is>
@@ -827,40 +854,43 @@
           <t>먼치킨</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="2" t="n">
+        <v>2140005</v>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>loaf</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="F8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="H8" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="J8" s="1" t="n">
         <v>50005</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="K8" s="1" t="n">
         <v>50015</v>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>다리가 짧아서 걷는 것보다 구르는 게 빠르다.</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/loaf</t>
         </is>
@@ -875,40 +905,43 @@
           <t>벵갈</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="2" t="n">
+        <v>2140006</v>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>ninja</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="F9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="G9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="H9" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="I9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="J9" s="1" t="n">
         <v>50006</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="K9" s="1" t="n">
         <v>50016</v>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>야생의 피가 흐른다. 눈 깜짝할 새 옆에 와 있다.</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/ninja</t>
         </is>
@@ -923,40 +956,43 @@
           <t>스핑크스</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="2" t="n">
+        <v>2140007</v>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>laser</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="E10" s="1" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="F10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="G10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="H10" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="I10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="J10" s="1" t="n">
         <v>50007</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="K10" s="1" t="n">
         <v>50017</v>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>털이 없는 대신 눈빛이 너무 강렬해서 물건이 깨진다.</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/laser</t>
         </is>
@@ -971,40 +1007,43 @@
           <t>메인쿤</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="2" t="n">
+        <v>2140008</v>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>gym</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="F11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="G11" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="H11" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="I11" s="1" t="n">
         <v>1.12</v>
       </c>
-      <c r="I11" s="1" t="n">
+      <c r="J11" s="1" t="n">
         <v>50008</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="K11" s="1" t="n">
         <v>50018</v>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>고양이계의 헤비급. 앞발 한 번이면 식탁이 흔들린다.</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/gym</t>
         </is>
@@ -1019,40 +1058,43 @@
           <t>마녀 모자 고양이</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="2" t="n">
+        <v>2140009</v>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>fire</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="E12" s="1" t="inlineStr">
         <is>
           <t>Special</t>
         </is>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="F12" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="G12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="H12" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="I12" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="I12" s="1" t="n">
+      <c r="J12" s="1" t="n">
         <v>50009</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="K12" s="1" t="n">
         <v>50019</v>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>할로윈 모자를 쓰더니 진짜로 마법을 쓰기 시작했다.</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/fire</t>
         </is>
@@ -1067,40 +1109,43 @@
           <t>우주복 고양이</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" s="2" t="n">
+        <v>2140010</v>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>space</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Special</t>
         </is>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="F13" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="G13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="H13" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="I13" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="I13" s="1" t="n">
+      <c r="J13" s="1" t="n">
         <v>50010</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="K13" s="1" t="n">
         <v>50020</v>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>어디서 우주복을 구했는지는 아무도 모른다. 무중력으로 에너지를 모은다.</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Cats/Parts/space</t>
         </is>
@@ -1117,12 +1162,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -1154,85 +1199,90 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>스킬 이름 키</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>조건1 타입</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>조건1 밸류_01</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>조건1 밸류_02</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>조건2 타입</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>조건2 밸류_01</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>조건2 밸류_02</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>효과 타입</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>밸류_01</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>밸류_02</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>밸류_03</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>밸류_04</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>밸류_05</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>밸류_06</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>시전 시간</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>쿨타임</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>스킬 아이콘</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>스킬 설명</t>
         </is>
@@ -1251,85 +1301,90 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t>skill_name_sk</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t>cond1_type</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>cond1_value_01</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>cond1_value_02</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>cond2_type</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>cond2_value_01</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>cond2_value_02</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>effect_type</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>value_01</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>value_02</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>value_03</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>value_04</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>value_05</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>value_06</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>cool_time</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>skill_icon</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>skill_explain</t>
         </is>
@@ -1348,85 +1403,90 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="O3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr">
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="P3" s="1" t="inlineStr">
+      <c r="Q3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="Q3" s="1" t="inlineStr">
+      <c r="R3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="R3" s="1" t="inlineStr">
+      <c r="S3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="S3" s="1" t="inlineStr">
+      <c r="T3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1441,42 +1501,42 @@
           <t>하악질</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>2250001</v>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="E4" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="F4" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="I4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>Hiss_Fear</t>
         </is>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="K4" s="1" t="n">
         <v>1.6</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="L4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" s="1" t="n">
         <v>0</v>
       </c>
@@ -1487,17 +1547,20 @@
         <v>0</v>
       </c>
       <c r="P4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="1" t="inlineStr">
+      <c r="R4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1" t="inlineStr">
         <is>
           <t>😾</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>3초 동안 쥐들이 겁먹는 범위 ×1.6</t>
         </is>
@@ -1512,42 +1575,42 @@
           <t>더블 냥펀치</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="n">
+        <v>2250002</v>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="E5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="F5" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G5" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
         <is>
           <t>Double_Pounce</t>
         </is>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="L5" s="1" t="n">
         <v>640</v>
       </c>
-      <c r="L5" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" s="1" t="n">
         <v>0</v>
       </c>
@@ -1558,17 +1621,20 @@
         <v>0</v>
       </c>
       <c r="P5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1" t="inlineStr">
+      <c r="R5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1" t="inlineStr">
         <is>
           <t>👊</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>다음 덮치기가 2연속</t>
         </is>
@@ -1583,42 +1649,42 @@
           <t>신사의 일격</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>2250003</v>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="E6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="F6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G6" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="I6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
         <is>
           <t>Crit_Pounce</t>
         </is>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="K6" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="L6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L6" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" s="1" t="n">
         <v>0</v>
       </c>
@@ -1629,17 +1695,20 @@
         <v>0</v>
       </c>
       <c r="P6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1" t="inlineStr">
+      <c r="R6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1" t="inlineStr">
         <is>
           <t>🎩</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>다음 덮치기가 크리티컬 (범위·기절 시간 증가)</t>
         </is>
@@ -1654,45 +1723,45 @@
           <t>털뭉치 프레스</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="2" t="n">
+        <v>2250004</v>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="E7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="F7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G7" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="I7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
         <is>
           <t>Jump_Press</t>
         </is>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="K7" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="L7" s="1" t="n">
         <v>1.8</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>380</v>
       </c>
-      <c r="M7" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" s="1" t="n">
         <v>0</v>
       </c>
@@ -1700,17 +1769,20 @@
         <v>0</v>
       </c>
       <c r="P7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1" t="inlineStr">
+      <c r="R7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1" t="inlineStr">
         <is>
           <t>☁️</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>높이 뛰어올라 쥐 쪽으로 깔아뭉개기, 주변 물건도 날림</t>
         </is>
@@ -1725,45 +1797,45 @@
           <t>식빵 굴리기</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="2" t="n">
+        <v>2250005</v>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="E8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="F8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G8" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="I8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
         <is>
           <t>Roll_Charge</t>
         </is>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="K8" s="1" t="n">
         <v>1.3</v>
       </c>
-      <c r="K8" s="1" t="n">
+      <c r="L8" s="1" t="n">
         <v>560</v>
       </c>
-      <c r="L8" s="1" t="n">
+      <c r="M8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="M8" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" s="1" t="n">
         <v>0</v>
       </c>
@@ -1771,17 +1843,20 @@
         <v>0</v>
       </c>
       <c r="P8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1" t="inlineStr">
+      <c r="R8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1" t="inlineStr">
         <is>
           <t>🍞</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>몸을 말고 쥐 쪽으로 데굴데굴 돌진, 닿은 쥐는 나뒹굴며 기절</t>
         </is>
@@ -1796,39 +1871,39 @@
           <t>그림자 순간이동</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="2" t="n">
+        <v>2250006</v>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="E9" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="F9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G9" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="inlineStr">
+      <c r="I9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
         <is>
           <t>Crowd_Teleport</t>
         </is>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="K9" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="K9" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" s="1" t="n">
         <v>0</v>
       </c>
@@ -1842,17 +1917,20 @@
         <v>0</v>
       </c>
       <c r="P9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1" t="inlineStr">
+      <c r="R9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1" t="inlineStr">
         <is>
           <t>🐆</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>쥐가 가장 많이 모인 곳 옆으로 순간이동 → 바로 덮치기</t>
         </is>
@@ -1867,45 +1945,45 @@
           <t>레이저 눈빛</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="2" t="n">
+        <v>2250007</v>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="E10" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="F10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G10" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="I10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
         <is>
           <t>Laser_Stun</t>
         </is>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="K10" s="1" t="n">
         <v>460</v>
       </c>
-      <c r="K10" s="1" t="n">
+      <c r="L10" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="L10" s="1" t="n">
+      <c r="M10" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="M10" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" s="1" t="n">
         <v>0</v>
       </c>
@@ -1913,17 +1991,20 @@
         <v>0</v>
       </c>
       <c r="P10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1" t="inlineStr">
+      <c r="R10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1" t="inlineStr">
         <is>
           <t>👁️</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>가장 가까운 쥐 방향으로 레이저, 맞은 쥐 기절</t>
         </is>
@@ -1938,45 +2019,45 @@
           <t>근육 과시</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="2" t="n">
+        <v>2250008</v>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="E11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="F11" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G11" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="I11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>Roar_Blast</t>
         </is>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="K11" s="1" t="n">
         <v>280</v>
       </c>
-      <c r="K11" s="1" t="n">
+      <c r="L11" s="1" t="n">
         <v>560</v>
       </c>
-      <c r="L11" s="1" t="n">
+      <c r="M11" s="1" t="n">
         <v>360</v>
       </c>
-      <c r="M11" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" s="1" t="n">
         <v>0</v>
       </c>
@@ -1984,17 +2065,20 @@
         <v>0</v>
       </c>
       <c r="P11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1" t="inlineStr">
+      <c r="R11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1" t="inlineStr">
         <is>
           <t>💪</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>포효로 주변 쥐와 물건을 사방으로 날려버림</t>
         </is>
@@ -2009,45 +2093,45 @@
           <t>불덩이 마법</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="2" t="n">
+        <v>2250009</v>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="E12" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="F12" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G12" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H12" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="I12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>Fireball</t>
         </is>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="K12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="K12" s="1" t="n">
+      <c r="L12" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="L12" s="1" t="n">
+      <c r="M12" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="M12" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" s="1" t="n">
         <v>0</v>
       </c>
@@ -2055,17 +2139,20 @@
         <v>0</v>
       </c>
       <c r="P12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1" t="inlineStr">
+      <c r="R12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>근처 쥐에게 불덩이 연속 발사</t>
         </is>
@@ -2080,63 +2167,66 @@
           <t>무중력 파동</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" s="2" t="n">
+        <v>2250010</v>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="E13" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="F13" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G13" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="I13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
         <is>
           <t>Gravity_Wave</t>
         </is>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="K13" s="1" t="n">
         <v>260</v>
       </c>
-      <c r="K13" s="1" t="n">
+      <c r="L13" s="1" t="n">
         <v>1.4</v>
       </c>
-      <c r="L13" s="1" t="n">
+      <c r="M13" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="N13" s="1" t="n">
         <v>750</v>
       </c>
-      <c r="N13" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="1" t="inlineStr">
+      <c r="R13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1" t="inlineStr">
         <is>
           <t>🌌</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>주변 쥐를 공중으로 띄우고 기절</t>
         </is>
@@ -2151,59 +2241,62 @@
           <t>냥냥 대폭격</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C14" s="2" t="n">
+        <v>2250011</v>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="E14" s="1" t="n">
         <v>2.5</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="F14" s="1" t="n">
         <v>3.5</v>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G14" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="I14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
         <is>
           <t>Crowd_Slam</t>
         </is>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="K14" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="K14" s="1" t="n">
+      <c r="L14" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L14" s="1" t="n">
+      <c r="M14" s="1" t="n">
         <v>0.55</v>
       </c>
-      <c r="M14" s="1" t="n">
+      <c r="N14" s="1" t="n">
         <v>0.35</v>
       </c>
-      <c r="N14" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O14" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="R14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>쥐가 가장 많이 모인 곳으로 뛰어올라 내려찍기, 범위 안 쥐 기절</t>
         </is>
@@ -2218,59 +2311,62 @@
           <t>냥펀치 연타</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C15" s="2" t="n">
+        <v>2250012</v>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="E15" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="F15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G15" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="I15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
         <is>
           <t>Crowd_Combo</t>
         </is>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="K15" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="K15" s="1" t="n">
+      <c r="L15" s="1" t="n">
         <v>1.3</v>
       </c>
-      <c r="L15" s="1" t="n">
+      <c r="M15" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="M15" s="1" t="n">
+      <c r="N15" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="N15" s="1" t="n">
+      <c r="O15" s="1" t="n">
         <v>0.22</v>
       </c>
-      <c r="O15" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="1" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="R15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>무리를 찾아 작은 내려찍기 3연속 (매번 새 무리를 노림)</t>
         </is>
@@ -2285,59 +2381,62 @@
           <t>급소 찌르기</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C16" s="2" t="n">
+        <v>2250013</v>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="E16" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="F16" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G16" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H16" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="1" t="inlineStr">
+      <c r="I16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
         <is>
           <t>Crowd_Pinpoint</t>
         </is>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="K16" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="K16" s="1" t="n">
+      <c r="L16" s="1" t="n">
         <v>3.2</v>
       </c>
-      <c r="L16" s="1" t="n">
+      <c r="M16" s="1" t="n">
         <v>0.35</v>
       </c>
-      <c r="M16" s="1" t="n">
+      <c r="N16" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="N16" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="1" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="R16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>좁지만 아주 빠르게, 오래 기절시키는 일격</t>
         </is>
@@ -2352,59 +2451,62 @@
           <t>뱃살 프레스</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C17" s="2" t="n">
+        <v>2250014</v>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="E17" s="1" t="n">
         <v>3.5</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="F17" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G17" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="1" t="inlineStr">
+      <c r="I17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
         <is>
           <t>Crowd_Belly</t>
         </is>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="K17" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="K17" s="1" t="n">
+      <c r="L17" s="1" t="n">
         <v>2.2</v>
       </c>
-      <c r="L17" s="1" t="n">
+      <c r="M17" s="1" t="n">
         <v>0.8</v>
       </c>
-      <c r="M17" s="1" t="n">
+      <c r="N17" s="1" t="n">
         <v>0.55</v>
       </c>
-      <c r="N17" s="1" t="n">
+      <c r="O17" s="1" t="n">
         <v>420</v>
       </c>
-      <c r="O17" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="P17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="1" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="R17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="1" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>아주 넓은 범위를 뱃살로 깔아뭉갬, 물건도 날아감</t>
         </is>
@@ -2419,59 +2521,62 @@
           <t>식빵 볼링</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C18" s="2" t="n">
+        <v>2250015</v>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="E18" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="F18" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G18" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="I18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
         <is>
           <t>Crowd_Roll</t>
         </is>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="K18" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="K18" s="1" t="n">
+      <c r="L18" s="1" t="n">
         <v>1.6</v>
       </c>
-      <c r="L18" s="1" t="n">
+      <c r="M18" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="M18" s="1" t="n">
+      <c r="N18" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="N18" s="1" t="n">
+      <c r="O18" s="1" t="n">
         <v>950</v>
       </c>
-      <c r="O18" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="P18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="1" t="inlineStr"/>
-      <c r="S18" s="2" t="inlineStr">
+      <c r="R18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>무리를 향해 데굴데굴 굴러 지나가는 쥐를 쓰러뜨리고 끝에서 쿵</t>
         </is>
@@ -2486,45 +2591,45 @@
           <t>그림자 습격</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C19" s="2" t="n">
+        <v>2250016</v>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="E19" s="1" t="n">
         <v>2.5</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="F19" s="1" t="n">
         <v>3.5</v>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G19" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="1" t="inlineStr">
+      <c r="I19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1" t="inlineStr">
         <is>
           <t>Crowd_Blink</t>
         </is>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="K19" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="K19" s="1" t="n">
+      <c r="L19" s="1" t="n">
         <v>1.8</v>
       </c>
-      <c r="L19" s="1" t="n">
+      <c r="M19" s="1" t="n">
         <v>0.35</v>
       </c>
-      <c r="M19" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="N19" s="1" t="n">
         <v>0</v>
       </c>
@@ -2532,13 +2637,16 @@
         <v>0</v>
       </c>
       <c r="P19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="1" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="R19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="1" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>연기처럼 사라졌다가 무리 한가운데 나타나 내려찍기 (거리 무관)</t>
         </is>
@@ -2553,59 +2661,62 @@
           <t>레이저 폭격</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C20" s="2" t="n">
+        <v>2250017</v>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="E20" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="F20" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G20" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="1" t="inlineStr">
+      <c r="I20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
         <is>
           <t>Crowd_Laser</t>
         </is>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="K20" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="K20" s="1" t="n">
+      <c r="L20" s="1" t="n">
         <v>2.4</v>
       </c>
-      <c r="L20" s="1" t="n">
+      <c r="M20" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="N20" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="N20" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="1" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr">
+      <c r="R20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>가만히 서서 쥐가 많은 곳 2군데에 하늘 레이저</t>
         </is>
@@ -2620,59 +2731,62 @@
           <t>지진 내려찍기</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C21" s="2" t="n">
+        <v>2250018</v>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="E21" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="F21" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G21" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="1" t="inlineStr">
+      <c r="I21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="inlineStr">
         <is>
           <t>Crowd_Quake</t>
         </is>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="K21" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="K21" s="1" t="n">
+      <c r="L21" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="L21" s="1" t="n">
+      <c r="M21" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="N21" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="N21" s="1" t="n">
+      <c r="O21" s="1" t="n">
         <v>80</v>
       </c>
-      <c r="O21" s="1" t="n">
+      <c r="P21" s="1" t="n">
         <v>0.18</v>
       </c>
-      <c r="P21" s="1" t="n">
+      <c r="Q21" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="1" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="R21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr">
         <is>
           <t>내려찍은 자리에서 충격파가 3겹으로 퍼짐</t>
         </is>
@@ -2687,59 +2801,62 @@
           <t>운석 마법</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C22" s="2" t="n">
+        <v>2250019</v>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="E22" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="F22" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G22" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H22" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="I22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
         <is>
           <t>Crowd_Meteor</t>
         </is>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="K22" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="K22" s="1" t="n">
+      <c r="L22" s="1" t="n">
         <v>1.8</v>
       </c>
-      <c r="L22" s="1" t="n">
+      <c r="M22" s="1" t="n">
         <v>0.7</v>
       </c>
-      <c r="M22" s="1" t="n">
+      <c r="N22" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="N22" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O22" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="1" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="R22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="1" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>쥐가 많은 곳 3군데에 운석 소환</t>
         </is>
@@ -2754,59 +2871,62 @@
           <t>블랙홀</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C23" s="2" t="n">
+        <v>2250020</v>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
         <is>
           <t>Interval</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="E23" s="1" t="n">
         <v>3.5</v>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="F23" s="1" t="n">
         <v>4.5</v>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G23" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="H23" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="1" t="inlineStr">
+      <c r="I23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
         <is>
           <t>Crowd_Vortex</t>
         </is>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="K23" s="1" t="n">
         <v>280</v>
       </c>
-      <c r="K23" s="1" t="n">
+      <c r="L23" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L23" s="1" t="n">
+      <c r="M23" s="1" t="n">
         <v>0.7</v>
       </c>
-      <c r="M23" s="1" t="n">
+      <c r="N23" s="1" t="n">
         <v>520</v>
       </c>
-      <c r="N23" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="O23" s="1" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="1" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="R23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr">
         <is>
           <t>무리 한가운데 블랙홀 → 쥐를 빨아들인 뒤 띄워서 기절</t>
         </is>

--- a/Data_Table/고양이 캐릭터 테이블.xlsx
+++ b/Data_Table/고양이 캐릭터 테이블.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Character" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Skill" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cond_Type" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Effect_Type" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Character" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cond_Type" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effect_Type" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
